--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overview'!$A$4:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$4:$G$229</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered'!$A$4:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Defects'!$A$4:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Questions'!$A$4:$C$13</definedName>
   </definedNames>
@@ -655,7 +655,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Decisions       4</t>
+          <t xml:space="preserve">    Decisions       5</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Performance Management (D-008: Option C — P0–P2 run PARALLEL to EP42 W1–W3)</t>
+          <t>Performance Management (D-008: Option C — P0–P2 run PARALLEL to EP42 W1–W3; requirements OPEN, P0 written)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9454,8 +9454,26 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>D-009</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 — the three shape questions for performance management.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Context: EP44's requirements exercise opened under D-008 (Option C). Three choices changed the shape of the build rather than its wording, so they were put to the owner with a recommended default each and an explicit note that none of them blocked. / # / Question / Default put to him / His answer / /---/---/---/---/ / 1 / Cycle cadence, and is it tied to the pay round? / Annual, mid-term check-in, independent of the pay round / "Once a year" — default confirmed / / 2 / Is probation a real cycle or just a label? / Just a label; no probation cycles, no probation screens / "No probation a real cycle" — read as no probation as a real cycle, i.e. default confirmed / / 3 / Does an employee see their manager's written assessment? / Yes, after the manager submits / "Yes" — default confirmed / ⚠ On (2), the reading is recorded because the phrasing was ambiguous. "No…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D8"/>
+  <autoFilter ref="A4:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overview'!$A$4:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$4:$G$229</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered'!$A$4:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered'!$A$4:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Defects'!$A$4:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Questions'!$A$4:$C$13</definedName>
@@ -641,14 +641,14 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Stories         225   (149 done, 1 in progress, 75 planned)</t>
+          <t xml:space="preserve">    Stories         225   (150 done, 1 in progress, 74 planned)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Delivered rows  6  (a story is only here if it has evidence)</t>
+          <t xml:space="preserve">    Delivered rows  7  (a story is only here if it has evidence)</t>
         </is>
       </c>
     </row>
@@ -8030,9 +8030,9 @@
           <t>KAN-207</t>
         </is>
       </c>
-      <c r="B198" s="11" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9317,8 +9317,35 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>KAN-207</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>pytest 4,882 · browser 110/110 · vacation 39/39</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>YES — see notes</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>The distinction holds in the schema, not just the prose: the expectation says what step 1.2 means here for anybody; the roadmap says what you specifically need to do. Versioned, never overwritten — a new version supersedes the previous one inside the same transaction so uq_esr_one_live can never see two live rows, and the old one stays readable; from/target coordinates and the author's name are denormalised on purpose, because resolving them live would silently re-target every historical roadmap the moment somebody is promoted. Acknowledgement records a DISCUSSION, not agreement (CFL-42-50): the button reads Confirm we discussed this, the state reads "Discussed on 14 March", the audit action is STEP_ROADMAP_DISCUSSION_CONFIRMED and its reason says explicitly that it is not agreement — only the subject may confirm, it is idempotent, and an unconfirmed roadmap is still live and blocks nothing, with the follow-up surfaced to the manager instead. The employee is notified, once, in-app — the owner's overrule of the BA's and UX's "no", because a roadmap nobody knows about delivers zero transparency; no email, retires on view (an FYI must not sit in the bell like an approval), sent after the commit, and carrying no step number and no pay. /my-ladder is main nav on job_architecture:r, seeded to every role — visible to the employee, not optional. ⚠ Closed a KAN-190 gap that was missed: the step-disclosure switch (companies.display_step_to_employee, default TRUE) was in KAN-190's criteria and never built; it is added here because this is the first surface that consumes it. With it off, A2 option (b) — the roadmap reads in full as "What the next set of expectations looks like", with no step number and no "you are here". No ratings, scores, readiness or likelihood anywhere, in either the migration or schema.sql — that boundary is what keeps this out of GDPR Art. 22 / EU AI Act territory, and the test parses the function body rather than grepping, because the docstring names the ban in order to state it. Verified in a browser end to end: a manager blocked from writing for an unassessed report (with the reason), 1.3 → 2.0 correctly crossing into the next level, the bell badge appearing for the employee, and the wording correct in both the pre- and post-confirmation states. 4,882 pytest · browser 110/110 · vacation 39/39. ⚠ NOT Ready until a human reviews the copy against R-17 — the Architect declined to certify, correctly: the risk is whether it reads as expectations rather than an assessment, and no test can see that. The SPM owns that review. / /</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E10"/>
+  <autoFilter ref="A4:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overview'!$A$4:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$4:$G$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$4:$G$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered'!$A$4:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Defects'!$A$4:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Questions'!$A$4:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Questions'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Stories         225   (150 done, 1 in progress, 74 planned)</t>
+          <t xml:space="preserve">    Stories         226   (150 done, 1 in progress, 75 planned)</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Open questions  5 of 9</t>
+          <t xml:space="preserve">    Open questions  7 of 11</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Performance Management (D-008: Option C — P0–P2 run PARALLEL to EP42 W1–W3; requirements OPEN, P0 written)</t>
+          <t>Performance Management (D-008: Option C; requirements OPEN, P0 written; ⚠ AMENDED BY A7 — goal types, milestones, the four-level scale, the enforced self-first ordering, and KAN-241 the readiness outcome)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>Goal/objective authoring by employee and manager, per cycle, versioned. Optional cascade from a parent goal — cascade is a link, never an automatic copy or an enforced target. Row-scoped: a manager sees their direct reports' goals and nobody else's. Audited.</t>
+          <t>⚠ A7: goals carry a type — BUSINESS or DEVELOPMENT — rendered as two named sections, not a tag; both are agreed with the employee at the start of the year and the agreement is recorded. Goal/objective authoring by employee and manager, per cycle, versioned. Optional cascade from a parent goal — cascade is a link, never an automatic copy or an enforced target. Row-scoped: a manager sees their direct reports' goals and nobody else's. Audited.</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>Narrative check-ins against a goal, timestamped, authored by either party, visible to both. No score, no percentage complete, no RAG, no automatic status. A completion percentage is a rating with a friendlier name and it is refused.</t>
+          <t>⚠ A7 — reframed as MILESTONES ACHIEVED: dated, authored by the employee, against a specific goal, visible to the manager, added throughout the year. Not approved one by one — a year-long approval queue is how this dies; the manager weighs them at review time. Narrative check-ins against a goal, timestamped, authored by either party, visible to both. No score, no percentage complete, no RAG, no automatic status. A completion percentage is a rating with a friendlier name and it is refused.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>Company-defined ordinal scale with authored labels and descriptions, versioned — a rating from 2027 must still be readable in 2029 against the scale that produced it. Nothing predetermined, nothing suggested: no shipped scale, no default point count, no "typical" wording. A company that has not authored a scale cannot open a cycle.</t>
+          <t>⚠ A7 — the owner's four labels ship as the DEFAULT scale: Below expectation · Meeting expectation · Above expectation · Beyond expectation. Still configurable and versioned as below. Company-defined ordinal scale with authored labels and descriptions, versioned — a rating from 2027 must still be readable in 2029 against the scale that produced it. Nothing predetermined, nothing suggested: no shipped scale, no default point count, no "typical" wording. A company that has not authored a scale cannot open a cycle.</t>
         </is>
       </c>
     </row>
@@ -9100,8 +9100,45 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>KAN-241</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>EP42 — Compensation, Job Architecture &amp; Pay Equity</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>KAN-241 — NEW STORY: the readiness outcome</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>Must · P1</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>As a manager and employee, I want the review to conclude with where this person stands on the ladder, so the outcome is stated rather than left implied.</t>
+        </is>
+      </c>
+      <c r="G230" s="8" t="inlineStr">
+        <is>
+          <t>A fixed three-value outcome, deliberately NOT company-configurable: FOCUS_ON_CURRENT_ROLE · READY_IN_12_24_MONTHS · READY_FOR_NEXT_LEVEL. Fixed because unlike the rating scale — which is about a period's work and is properly a company's own vocabulary — these three are structurally tied to the product's own promotion mechanism (stay / progressing / level change), and a tenant renaming them would break the link to KAN-197. Recorded as the conclusion of the discussion, not before it: it is an outcome of a conversation, which is what the owner described. READY_FOR_NEXT_LEVEL NEVER auto-creates anything. It is a stated view that a human then acts on by raising a level change through the…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G229"/>
+  <autoFilter ref="A4:G230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9736,7 +9773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9928,8 +9965,42 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>OQ-10</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>&gt; OQ-10 — what happens if the employee never submits their self-assessment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>OQ-11</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>&gt; OQ-11 — may a goal be "partially achieved"?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:C13"/>
+  <autoFilter ref="A4:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -669,7 +669,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Open questions  7 of 11</t>
+          <t xml:space="preserve">    Open questions  5 of 11</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>Self-assessment per cycle against the company's form. Visible to the manager on submission; the manager's assessment is not visible to the employee until the cycle reaches its release point, so a self-assessment is not anchored by a rating already given. Versioned; the employee may amend before submission and not after.</t>
+          <t>⚠ A7 + OQ-10: the employee submits a narrative AND their own rating, and that submission GATES the manager's rating (not merely its visibility). The cycle carries a self-assessment deadline; after it HR — never the manager — may record SELF_ASSESSMENT_NOT_SUBMITTED, the employee is notified, and the manager may proceed. "Did not submit" and "submitted with nothing in it" must never render the same — one is an absence, the other a statement. A late submission is accepted and does not erase the fact. Self-assessment per cycle against the company's form. Visible to the manager on submission; the manager's assessment is not visible to the employee until the cycle reaches its release point, so…</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>Manager assessment per employee per cycle, row-scoped to direct reports. Cites the goals from KAN-221 and, where one exists, the step roadmap from EP42's KAN-207 — the owner's own narrative link ("the expectation from the employee is if they satisfy in next level the compensation review based on that") made visible rather than implied. Audited; versioned.</t>
+          <t>⚠ A7 + OQ-11: per goal an outcome — ACHIEVED · PARTIALLY_ACHIEVED · NOT_ACHIEVED — plus a comment; then an overall rating. The overall rating is NEVER computed from the per-goal outcomes and no suggested rating may appear on the screen — a suggestion is a computed decision with a human rubber-stamping it. Blocked until the employee has submitted or HR has recorded not-submitted, and the block says which. Manager assessment per employee per cycle, row-scoped to direct reports. Cites the goals from KAN-221 and, where one exists, the step roadmap from EP42's KAN-207 — the owner's own narrative link ("the expectation from the employee is if they satisfy in next level the compensation review…</t>
         </is>
       </c>
     </row>
@@ -9973,12 +9973,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>&gt; OQ-10 — what happens if the employee never submits their self-assessment?</t>
+          <t>&gt; OQ-10 — ✅ ANSWERED 10 Aug 2026: introduce a submission deadline. His words: *"Introduce a</t>
         </is>
       </c>
     </row>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>&gt; OQ-11 — may a goal be "partially achieved"?</t>
+          <t>&gt; OQ-11 — ✅ ANSWERED 10 Aug 2026: three values. His words: *"Achieved / Partially achieved / Not</t>
         </is>
       </c>
     </row>

--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Overview'!$A$4:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$4:$G$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Delivered'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$4:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Defects'!$A$4:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Questions'!$A$4:$C$15</definedName>
   </definedNames>
@@ -655,7 +655,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Decisions       5</t>
+          <t xml:space="preserve">    Decisions       6</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Compensation, Job Architecture &amp; Pay Equity</t>
+          <t>Compensation, Job Architecture &amp; Pay Equity (W0+W1 ✅ done; W2–W4 follow EP44 per D-010)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Performance Management (D-008: Option C; requirements OPEN, P0 written; ⚠ AMENDED BY A7 — goal types, milestones, the four-level scale, the enforced self-first ordering, and KAN-241 the readiness outcome)</t>
+          <t>Performance Management (⚠ D-010 — BUILT FIRST, compensation follows; requirements OPEN, P0 written; ⚠ AMENDED BY A7 — goal types, milestones, the four-level scale, the enforced self-first ordering, and KAN-241 the readiness outcome)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -9393,7 +9393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>## SEQUENCING — where performance management goes (Decision D-008 — RESOLVED: Option C)</t>
+          <t>## SEQUENCING — where performance management goes (D-008: Option C — ⚠ SUPERSEDED BY D-010, sequential)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr"/>
@@ -9536,8 +9536,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>D-010</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-10 — performance is built FIRST; compensation follows it.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Proceed with Performance Review development</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>His words: "Proceed with Performance Review development. I'll review and sign off the roadmap wording separately. Compensation can follow after the performance module is completed." This supersedes the parallelism in D-008 (Option C). Option C ran performance P0–P2 alongside compensation W1–W3, on the assumption of extra capacity. The order is now sequential: the performance module completes, then compensation W2–W4. Read as: performance entirely before the remaining compensation waves — not "performance first within the parallel plan". Flagged, because the two readings differ by about a quarter. He has also decoupled the KAN-207 copy sign-off from the critical path by taking it himself, which is what lets this proceed today. What it costs, stated once and not re-litigated: EP42 W2 was the minimum shippable slice — pay markets, what each step is worth, and…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D9"/>
+  <autoFilter ref="A4:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/project-management/PROGRAMME_TRACKER.xlsx
+++ b/docs/project-management/PROGRAMME_TRACKER.xlsx
@@ -641,7 +641,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Stories         226   (150 done, 1 in progress, 75 planned)</t>
+          <t xml:space="preserve">    Stories         226   (152 done, 1 in progress, 73 planned)</t>
         </is>
       </c>
     </row>
@@ -8380,9 +8380,9 @@
           <t>KAN-219</t>
         </is>
       </c>
-      <c r="B208" s="11" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
@@ -8413,9 +8413,9 @@
           <t>KAN-220</t>
         </is>
       </c>
-      <c r="B209" s="11" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
